--- a/src/assets/mission/sonede.xlsx
+++ b/src/assets/mission/sonede.xlsx
@@ -431,7 +431,7 @@
         <v>2026-10-03</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>Projet de redondance de la station de dessalement d’eau</v>
       </c>
     </row>
   </sheetData>
@@ -443,10 +443,523 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:J16"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>missionId</v>
+      </c>
+      <c r="B1" t="str">
+        <v>lotId</v>
+      </c>
+      <c r="C1" t="str">
+        <v>lotNom</v>
+      </c>
+      <c r="D1" t="str">
+        <v>lotDescription</v>
+      </c>
+      <c r="E1" t="str">
+        <v>tacheId</v>
+      </c>
+      <c r="F1" t="str">
+        <v>tacheNom</v>
+      </c>
+      <c r="G1" t="str">
+        <v>dateDebut</v>
+      </c>
+      <c r="H1" t="str">
+        <v>dateFin</v>
+      </c>
+      <c r="I1" t="str">
+        <v>description</v>
+      </c>
+      <c r="J1" t="str">
+        <v>avancement</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B2" t="str">
+        <v>mudxqxh6-ds4zrl</v>
+      </c>
+      <c r="C2" t="str">
+        <v>déplacement  et livraison marchandise</v>
+      </c>
+      <c r="D2" t="str">
+        <v xml:space="preserve">déplacer vers jerba et livrée les armoires électrique et prendre le bl avec décharge </v>
+      </c>
+      <c r="E2" t="str">
+        <v>mudxrho9-2whl0l</v>
+      </c>
+      <c r="F2" t="str">
+        <v>deplacement vers jerba et jarzis</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B3" t="str">
+        <v>mudxqxh6-ds4zrl</v>
+      </c>
+      <c r="C3" t="str">
+        <v>déplacement  et livraison marchandise</v>
+      </c>
+      <c r="D3" t="str">
+        <v xml:space="preserve">déplacer vers jerba et livrée les armoires électrique et prendre le bl avec décharge </v>
+      </c>
+      <c r="E3" t="str">
+        <v>mudxs0nl-xicpta</v>
+      </c>
+      <c r="F3" t="str">
+        <v>livraison des armoire électriques</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B4" t="str">
+        <v>mudxqxh6-ds4zrl</v>
+      </c>
+      <c r="C4" t="str">
+        <v>déplacement  et livraison marchandise</v>
+      </c>
+      <c r="D4" t="str">
+        <v xml:space="preserve">déplacer vers jerba et livrée les armoires électrique et prendre le bl avec décharge </v>
+      </c>
+      <c r="E4" t="str">
+        <v>mudxsn8i-brqq4e</v>
+      </c>
+      <c r="F4" t="str">
+        <v>bl avec decharge</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B5" t="str">
+        <v>mudxte55-q04hvo</v>
+      </c>
+      <c r="C5" t="str">
+        <v>fixation des armoire et chemin du câble Gallela</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v>mudxu5oh-28nv31</v>
+      </c>
+      <c r="F5" t="str">
+        <v>fixation des armoire</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="H5" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B6" t="str">
+        <v>mudxte55-q04hvo</v>
+      </c>
+      <c r="C6" t="str">
+        <v>fixation des armoire et chemin du câble Gallela</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v>mudxunvu-qqw21s</v>
+      </c>
+      <c r="F6" t="str">
+        <v>fixation chemin du cable</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="H6" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B7" t="str">
+        <v>mudxvhcq-b5fvwn</v>
+      </c>
+      <c r="C7" t="str">
+        <v>tirage du câble et repérage gallela</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v>mudxvxrm-v6p56k</v>
+      </c>
+      <c r="F7" t="str">
+        <v>tirage du câble</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="H7" t="str">
+        <v>2026-09-25</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B8" t="str">
+        <v>mudxvhcq-b5fvwn</v>
+      </c>
+      <c r="C8" t="str">
+        <v>tirage du câble et repérage gallela</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v>mudxwqt6-z2pc0e</v>
+      </c>
+      <c r="F8" t="str">
+        <v>repérage avec embouts du cable</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2026-09-25</v>
+      </c>
+      <c r="H8" t="str">
+        <v>2026-09-25</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B9" t="str">
+        <v>mudxxqxu-izbag9</v>
+      </c>
+      <c r="C9" t="str">
+        <v>branchement et mise en service gallela</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v>mudxy8r6-0g0qoh</v>
+      </c>
+      <c r="F9" t="str">
+        <v>branchement du capteur</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2026-09-25</v>
+      </c>
+      <c r="H9" t="str">
+        <v>2026-09-26</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B10" t="str">
+        <v>mudxxqxu-izbag9</v>
+      </c>
+      <c r="C10" t="str">
+        <v>branchement et mise en service gallela</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v>mudxyne2-ae9u7n</v>
+      </c>
+      <c r="F10" t="str">
+        <v>mise en service</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2026-09-26</v>
+      </c>
+      <c r="H10" t="str">
+        <v>2026-09-26</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B11" t="str">
+        <v>mudy2z5p-goypko</v>
+      </c>
+      <c r="C11" t="str">
+        <v>fixation des armoire et chemin du câble jarzis</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v>mudy705p-pd7exl</v>
+      </c>
+      <c r="F11" t="str">
+        <v>fixation des armoire</v>
+      </c>
+      <c r="G11" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="H11" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B12" t="str">
+        <v>mudy2z5p-goypko</v>
+      </c>
+      <c r="C12" t="str">
+        <v>fixation des armoire et chemin du câble jarzis</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v>mudy7lbg-758svu</v>
+      </c>
+      <c r="F12" t="str">
+        <v>fixation chemin du cable</v>
+      </c>
+      <c r="G12" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="H12" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B13" t="str">
+        <v>mudy33ar-k7kc3e</v>
+      </c>
+      <c r="C13" t="str">
+        <v>tirage du câble et repérage jarzis</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v>mudy8btw-4c42kq</v>
+      </c>
+      <c r="F13" t="str">
+        <v>tirage du câble</v>
+      </c>
+      <c r="G13" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="H13" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B14" t="str">
+        <v>mudy33ar-k7kc3e</v>
+      </c>
+      <c r="C14" t="str">
+        <v>tirage du câble et repérage jarzis</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v>mudy8vas-8k0swd</v>
+      </c>
+      <c r="F14" t="str">
+        <v>repérage avec embouts du cable</v>
+      </c>
+      <c r="G14" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="H14" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B15" t="str">
+        <v>mudy379n-pfffdf</v>
+      </c>
+      <c r="C15" t="str">
+        <v>branchement et mise en service jarzis</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v>mudy9k1p-a8f045</v>
+      </c>
+      <c r="F15" t="str">
+        <v>branchement du capteur</v>
+      </c>
+      <c r="G15" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="H15" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B16" t="str">
+        <v>mudy379n-pfffdf</v>
+      </c>
+      <c r="C16" t="str">
+        <v>branchement et mise en service jarzis</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v>mudya0l8-c4j4p6</v>
+      </c>
+      <c r="F16" t="str">
+        <v>mise en service</v>
+      </c>
+      <c r="G16" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="H16" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/assets/mission/sonede.xlsx
+++ b/src/assets/mission/sonede.xlsx
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -593,7 +593,7 @@
         <v>fixation des armoire</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-25</v>
       </c>
       <c r="H5" t="str">
         <v>2026-09-23</v>
@@ -602,7 +602,7 @@
         <v/>
       </c>
       <c r="J5">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -625,7 +625,7 @@
         <v>fixation chemin du cable</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="H6" t="str">
         <v>2026-09-23</v>
@@ -634,7 +634,7 @@
         <v/>
       </c>
       <c r="J6">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -657,16 +657,16 @@
         <v>tirage du câble</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-21</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-09-25</v>
+        <v>2026-10-01</v>
       </c>
       <c r="I7" t="str">
         <v/>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -689,16 +689,16 @@
         <v>repérage avec embouts du cable</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-09-25</v>
+        <v>2026-09-28</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-09-25</v>
+        <v>2026-10-02</v>
       </c>
       <c r="I8" t="str">
         <v/>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -721,10 +721,10 @@
         <v>branchement du capteur</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-09-25</v>
+        <v>2026-09-30</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-09-26</v>
+        <v>2026-10-02</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -753,10 +753,10 @@
         <v>mise en service</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-09-26</v>
+        <v>2026-10-01</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-09-26</v>
+        <v>2026-10-02</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -785,10 +785,10 @@
         <v>fixation des armoire</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-05</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-08</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -817,10 +817,10 @@
         <v>fixation chemin du cable</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-05</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-10</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -849,10 +849,10 @@
         <v>tirage du câble</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-10</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-10-01</v>
+        <v>2026-11-14</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v>branchement du capteur</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-15</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-17</v>
       </c>
       <c r="I15" t="str">
         <v/>

--- a/src/assets/mission/sonede.xlsx
+++ b/src/assets/mission/sonede.xlsx
@@ -443,7 +443,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -526,7 +526,7 @@
         <v>mudxs0nl-xicpta</v>
       </c>
       <c r="F3" t="str">
-        <v>livraison des armoire électriques</v>
+        <v>livraison des armoire électriques avec decharge</v>
       </c>
       <c r="G3" t="str">
         <v>2026-09-21</v>
@@ -546,25 +546,25 @@
         <v>muconu2l-3lm6qg</v>
       </c>
       <c r="B4" t="str">
-        <v>mudxqxh6-ds4zrl</v>
+        <v>mudxte55-q04hvo</v>
       </c>
       <c r="C4" t="str">
-        <v>déplacement  et livraison marchandise</v>
+        <v>fixation des armoire et chemin du câble Gallela</v>
       </c>
       <c r="D4" t="str">
-        <v xml:space="preserve">déplacer vers jerba et livrée les armoires électrique et prendre le bl avec décharge </v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>mudxsn8i-brqq4e</v>
+        <v>mudxu5oh-28nv31</v>
       </c>
       <c r="F4" t="str">
-        <v>bl avec decharge</v>
+        <v>fixation armoire 1</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-25</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-25</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -587,16 +587,16 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>mudxu5oh-28nv31</v>
+        <v>mupqkz2m-ft11gi</v>
       </c>
       <c r="F5" t="str">
-        <v>fixation des armoire</v>
+        <v>Fixation aremoire 2</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-09-25</v>
+        <v>2026-09-26</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-26</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -619,22 +619,22 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>mudxunvu-qqw21s</v>
+        <v>mupqlswl-l02t2j</v>
       </c>
       <c r="F6" t="str">
-        <v>fixation chemin du cable</v>
+        <v>fixation armoire 3</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-09-23</v>
+        <v>2026-10-26</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-09-23</v>
+        <v>2026-10-26</v>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -642,31 +642,31 @@
         <v>muconu2l-3lm6qg</v>
       </c>
       <c r="B7" t="str">
-        <v>mudxvhcq-b5fvwn</v>
+        <v>mudxte55-q04hvo</v>
       </c>
       <c r="C7" t="str">
-        <v>tirage du câble et repérage gallela</v>
+        <v>fixation des armoire et chemin du câble Gallela</v>
       </c>
       <c r="D7" t="str">
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>mudxvxrm-v6p56k</v>
+        <v>mupqmnsm-o1moce</v>
       </c>
       <c r="F7" t="str">
-        <v>tirage du câble</v>
+        <v>chemin du câble salle 1</v>
       </c>
       <c r="G7" t="str">
         <v>2026-09-21</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-23</v>
       </c>
       <c r="I7" t="str">
         <v/>
       </c>
       <c r="J7">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -674,31 +674,31 @@
         <v>muconu2l-3lm6qg</v>
       </c>
       <c r="B8" t="str">
-        <v>mudxvhcq-b5fvwn</v>
+        <v>mudxte55-q04hvo</v>
       </c>
       <c r="C8" t="str">
-        <v>tirage du câble et repérage gallela</v>
+        <v>fixation des armoire et chemin du câble Gallela</v>
       </c>
       <c r="D8" t="str">
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>mudxwqt6-z2pc0e</v>
+        <v>mupqtrsf-wpccxx</v>
       </c>
       <c r="F8" t="str">
-        <v>repérage avec embouts du cable</v>
+        <v>chemin du câble salle 2</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-24</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-26</v>
       </c>
       <c r="I8" t="str">
         <v/>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -706,31 +706,31 @@
         <v>muconu2l-3lm6qg</v>
       </c>
       <c r="B9" t="str">
-        <v>mudxxqxu-izbag9</v>
+        <v>mudxte55-q04hvo</v>
       </c>
       <c r="C9" t="str">
-        <v>branchement et mise en service gallela</v>
+        <v>fixation des armoire et chemin du câble Gallela</v>
       </c>
       <c r="D9" t="str">
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>mudxy8r6-0g0qoh</v>
+        <v>mupqu5ry-dzee4f</v>
       </c>
       <c r="F9" t="str">
-        <v>branchement du capteur</v>
+        <v>chemin du câble salle 3</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-09-30</v>
+        <v>2026-09-29</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-01</v>
       </c>
       <c r="I9" t="str">
         <v/>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -738,25 +738,25 @@
         <v>muconu2l-3lm6qg</v>
       </c>
       <c r="B10" t="str">
-        <v>mudxxqxu-izbag9</v>
+        <v>mudxte55-q04hvo</v>
       </c>
       <c r="C10" t="str">
-        <v>branchement et mise en service gallela</v>
+        <v>fixation des armoire et chemin du câble Gallela</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>mudxyne2-ae9u7n</v>
+        <v>mupqupdr-kwffep</v>
       </c>
       <c r="F10" t="str">
-        <v>mise en service</v>
+        <v>chemin du câble salle 4</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-03</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -770,31 +770,31 @@
         <v>muconu2l-3lm6qg</v>
       </c>
       <c r="B11" t="str">
-        <v>mudy2z5p-goypko</v>
+        <v>mudxte55-q04hvo</v>
       </c>
       <c r="C11" t="str">
-        <v>fixation des armoire et chemin du câble jarzis</v>
+        <v>fixation des armoire et chemin du câble Gallela</v>
       </c>
       <c r="D11" t="str">
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>mudy705p-pd7exl</v>
+        <v>mupqvajd-mfmbu7</v>
       </c>
       <c r="F11" t="str">
-        <v>fixation des armoire</v>
+        <v>finition du chemain du cable</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-01</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-02</v>
       </c>
       <c r="I11" t="str">
         <v/>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -802,31 +802,31 @@
         <v>muconu2l-3lm6qg</v>
       </c>
       <c r="B12" t="str">
-        <v>mudy2z5p-goypko</v>
+        <v>mudxvhcq-b5fvwn</v>
       </c>
       <c r="C12" t="str">
-        <v>fixation des armoire et chemin du câble jarzis</v>
+        <v>tirage du câble et repérage gallela</v>
       </c>
       <c r="D12" t="str">
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>mudy7lbg-758svu</v>
+        <v>mudxvxrm-v6p56k</v>
       </c>
       <c r="F12" t="str">
-        <v>fixation chemin du cable</v>
+        <v>tirage du câble</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-10-05</v>
+        <v>2026-09-21</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-10-10</v>
+        <v>2026-10-01</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>1700 m et reste 950 m</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -834,31 +834,31 @@
         <v>muconu2l-3lm6qg</v>
       </c>
       <c r="B13" t="str">
-        <v>mudy33ar-k7kc3e</v>
+        <v>mudxvhcq-b5fvwn</v>
       </c>
       <c r="C13" t="str">
-        <v>tirage du câble et repérage jarzis</v>
+        <v>tirage du câble et repérage gallela</v>
       </c>
       <c r="D13" t="str">
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>mudy8btw-4c42kq</v>
+        <v>mudxwqt6-z2pc0e</v>
       </c>
       <c r="F13" t="str">
-        <v>tirage du câble</v>
+        <v>repérage avec embouts du cable</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-10-10</v>
+        <v>2026-09-28</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-11-14</v>
+        <v>2026-10-02</v>
       </c>
       <c r="I13" t="str">
         <v/>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -866,31 +866,31 @@
         <v>muconu2l-3lm6qg</v>
       </c>
       <c r="B14" t="str">
-        <v>mudy33ar-k7kc3e</v>
+        <v>mudxvhcq-b5fvwn</v>
       </c>
       <c r="C14" t="str">
-        <v>tirage du câble et repérage jarzis</v>
+        <v>tirage du câble et repérage gallela</v>
       </c>
       <c r="D14" t="str">
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>mudy8vas-8k0swd</v>
+        <v>mupqx4q8-zbxw64</v>
       </c>
       <c r="F14" t="str">
-        <v>repérage avec embouts du cable</v>
+        <v>layout et plan</v>
       </c>
       <c r="G14" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="H14" t="str">
         <v>2026-09-30</v>
       </c>
-      <c r="H14" t="str">
-        <v>2026-10-01</v>
-      </c>
       <c r="I14" t="str">
-        <v/>
+        <v>lay-out descriptive</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -898,31 +898,31 @@
         <v>muconu2l-3lm6qg</v>
       </c>
       <c r="B15" t="str">
-        <v>mudy379n-pfffdf</v>
+        <v>muputinm-rflw2m</v>
       </c>
       <c r="C15" t="str">
-        <v>branchement et mise en service jarzis</v>
+        <v>mise en service</v>
       </c>
       <c r="D15" t="str">
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>mudy9k1p-a8f045</v>
+        <v>muputznt-37aa21</v>
       </c>
       <c r="F15" t="str">
-        <v>branchement du capteur</v>
+        <v>backup</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-10-15</v>
+        <v>2026-09-23</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-10-17</v>
+        <v>2026-10-24</v>
       </c>
       <c r="I15" t="str">
         <v/>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -930,25 +930,25 @@
         <v>muconu2l-3lm6qg</v>
       </c>
       <c r="B16" t="str">
-        <v>mudy379n-pfffdf</v>
+        <v>muputinm-rflw2m</v>
       </c>
       <c r="C16" t="str">
-        <v>branchement et mise en service jarzis</v>
+        <v>mise en service</v>
       </c>
       <c r="D16" t="str">
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>mudya0l8-c4j4p6</v>
+        <v>mupuusui-kzv3q9</v>
       </c>
       <c r="F16" t="str">
-        <v>mise en service</v>
+        <v>chargement du configuration materielle</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-10-02</v>
+        <v>2026-10-05</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-05</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -957,9 +957,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>muconu2l-3lm6qg</v>
+      </c>
+      <c r="B17" t="str">
+        <v>muputinm-rflw2m</v>
+      </c>
+      <c r="C17" t="str">
+        <v>mise en service</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v>mupuvtf5-oqrbjs</v>
+      </c>
+      <c r="F17" t="str">
+        <v>changement des adresse</v>
+      </c>
+      <c r="G17" t="str">
+        <v>2026-10-06</v>
+      </c>
+      <c r="H17" t="str">
+        <v>2026-10-06</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J17"/>
   </ignoredErrors>
 </worksheet>
 </file>